--- a/parameters/UA/hydrogen/pipeline_parameters.xlsx
+++ b/parameters/UA/hydrogen/pipeline_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/mans3904_ox_ac_uk/Documents/DPhil/GEOH2-private/Parameters/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2859\Desktop\Geo-X\Geo-X\parameters\UA\hydrogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{0F17CB98-0437-854B-8C4B-CA3D4C7F5EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{781A8BF8-3C71-41AD-8549-C21EB804F0B9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41044B09-BD62-4865-B639-7DEFF0891E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{94028C1A-34CC-4B53-868B-8FD234C28ADF}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{94028C1A-34CC-4B53-868B-8FD234C28ADF}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="1" r:id="rId1"/>
@@ -130,9 +130,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -170,7 +170,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -276,7 +276,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -418,7 +418,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -427,17 +427,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0432B26-F3F0-43E1-A0D6-6197719E0B28}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -445,7 +445,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -453,7 +453,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -461,7 +461,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -469,7 +469,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -477,7 +477,7 @@
         <v>6.1381900000000004E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -485,7 +485,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -493,7 +493,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -509,17 +509,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3769E0-8D26-4542-AE82-68EE05500E52}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -528,7 +528,7 @@
         <v>2800000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -537,7 +537,7 @@
         <v>620000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -553,17 +553,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0FBB5F-3E9B-4EE5-99BF-10A517EB976F}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -572,7 +572,7 @@
         <v>2200000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -581,7 +581,7 @@
         <v>310000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -597,26 +597,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13374701-BB04-4EB3-9B4E-2501A6D51514}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <f>0.09 * 1000000</f>
-        <v>90000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <f>1.5 * 1000000</f>
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -625,7 +625,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
